--- a/data/ams_weekly_data/Tonor/business_report_week27.xlsx
+++ b/data/ams_weekly_data/Tonor/business_report_week27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,9 +554,13 @@
           <t>B01ISNU3X4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -568,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1183</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -586,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -598,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>45597.36</v>
+        <v>47206.68</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -631,9 +635,13 @@
           <t>B078WNW4YW</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -645,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -708,9 +716,13 @@
           <t>B07GVGMW59</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -722,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>682</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -740,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -752,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>29519.4</v>
+        <v>34093.98</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -862,9 +874,13 @@
           <t>B07WLWN2ZT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TC-777</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -876,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>917</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -939,9 +955,13 @@
           <t>B082W4B7SX</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -953,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -971,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -983,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1927.97</v>
+        <v>4003.39</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1016,9 +1036,13 @@
           <t>B089FVQD3Z</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1030,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1048,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1060,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2372.03</v>
+        <v>4744.06</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1075,27 +1099,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBA77104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TC30</t>
+          <t>TC20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B089SJGQBH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>B089SJGQBH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TC20</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1107,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1125,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1137,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>29350.86</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1152,27 +1180,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA77110</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TM20</t>
+          <t>TC30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>B08CVP2HXP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TC30</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1184,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1202,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1214,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>17697.47</v>
+        <v>29350.86</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1229,27 +1261,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79576</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TC30S+</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>B08NDB5NWP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TM20</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1261,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>657</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1279,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1291,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>22780.52</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1306,27 +1342,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79111</t>
+          <t>FBA77115</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TD510</t>
+          <t>TC40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>B08V1JS3NY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TC40</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1338,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1356,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1368,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>13428.8</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1383,27 +1423,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79113</t>
+          <t>FBA77103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TC310</t>
+          <t>ORCA001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>B09Z5Q194D</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ORCA001</t>
+        </is>
+      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1415,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1433,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1445,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1948.31</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1460,27 +1504,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA79574</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TC-777 PRO</t>
+          <t>TC30S</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>B0B4WTHLX5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TC30S</t>
+        </is>
+      </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1492,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1510,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1522,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>32568.64</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1537,27 +1585,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79114</t>
+          <t>FBA77116</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TC310+</t>
+          <t>TC40S</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>B0BBL47VR5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TC40S</t>
+        </is>
+      </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1569,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1587,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1599,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>7116.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1614,27 +1666,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79576</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TC30S+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>B0BRCR2QQ7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TC30S+</t>
+        </is>
+      </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1646,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1664,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1676,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3472.88</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1691,27 +1747,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA79111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t>TD510</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>B0BRKFP94K</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TD510</t>
+        </is>
+      </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1723,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1741,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1753,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1863.56</v>
+        <v>13428.8</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1768,27 +1828,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>TC310</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>B0BTCXQQ6M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TC310</t>
+        </is>
+      </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1800,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1818,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1830,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>12882.19</v>
+        <v>1948.31</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1845,77 +1909,648 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>FBK77102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0BVHZ5MKZ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B0BVHZ5MKZ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBA79116</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC-777 PRO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0BYHHSLPC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B0BYHHSLPC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TC-777 PRO</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>740</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1129</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>35990.67</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBA79114</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TC310+</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0CCV74CL7</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B0CCV74CL7</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TC310+</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>170</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>245</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7116.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FBA79585</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>T20LP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>T20LP</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>153</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>211</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7030.51</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FBA79586</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TRL-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0CH9JR3HL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B0CH9JR3HL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TRL-20</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2117.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FBA79696</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TD310+</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0CQX3VB1R</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B0CQX3VB1R</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TD310+</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>105</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>160</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1863.56</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FBA79697</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TD310</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0CQX4K9P5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B0CQX4K9P5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TD310</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>442</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>686</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>12882.19</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>FBA79577</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>TM310</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>B0CSCT63BL</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>B0CSCT63BL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1948.31</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TM310</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>246</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>321</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3981.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>0</v>
       </c>
     </row>
